--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA05801-0579-47B2-865B-90B42165D64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB07F3A-4861-4384-B651-C2DA8A41C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -517,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K5929"/>
+  <dimension ref="B1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -532,39 +532,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>34</v>
       </c>
@@ -593,7 +593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>34</v>
       </c>
@@ -622,7 +622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
@@ -651,14 +651,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="K5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>34</v>
       </c>
@@ -687,7 +687,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>34</v>
       </c>
@@ -716,7 +716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>34</v>
       </c>
@@ -745,7 +745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -774,7 +774,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>34</v>
       </c>
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -832,14 +832,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H12" s="2"/>
       <c r="I12" s="1"/>
       <c r="K12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>34</v>
       </c>
@@ -868,7 +868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>34</v>
       </c>
@@ -897,7 +897,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="K16" t="s">

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB07F3A-4861-4384-B651-C2DA8A41C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C21E9EE-15F3-401B-A437-3C797A932D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="36">
   <si>
     <t>Company Name</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>T Miller</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="H45" s="2">
-        <v>7.3495370370370372E-3</v>
+        <v>9.8379629629629633E-3</v>
       </c>
       <c r="I45" s="1">
         <v>46083.800347222219</v>
@@ -2050,98 +2053,373 @@
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H57" s="2"/>
-      <c r="I57" s="1"/>
+      <c r="B57" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57">
+        <v>5003</v>
+      </c>
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="2">
+        <v>2.3159722222222224E-2</v>
+      </c>
+      <c r="I57" s="1">
+        <v>46118.798495370371</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H58" s="2"/>
-      <c r="I58" s="1"/>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58">
+        <v>4996</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="2">
+        <v>7.3263888888888892E-3</v>
+      </c>
+      <c r="I58" s="1">
+        <v>46118.798495370371</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H59" s="2"/>
-      <c r="I59" s="1"/>
+      <c r="B59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59">
+        <v>5000</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1">
+        <v>46118.799189814818</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H60" s="2"/>
-      <c r="I60" s="1"/>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60">
+        <v>5004</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
+        <v>46118.799189814818</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H61" s="2"/>
-      <c r="I61" s="1"/>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61">
+        <v>5001</v>
+      </c>
+      <c r="D61" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="2">
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="I61" s="1">
+        <v>46118.799884259257</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H62" s="2"/>
-      <c r="I62" s="1"/>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62">
+        <v>4995</v>
+      </c>
+      <c r="D62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="2">
+        <v>8.0902777777777778E-3</v>
+      </c>
+      <c r="I62" s="1">
+        <v>46118.800578703704</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H63" s="2"/>
-      <c r="I63" s="1"/>
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63">
+        <v>4998</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="2">
+        <v>7.3032407407407404E-3</v>
+      </c>
+      <c r="I63" s="1">
+        <v>46118.800578703704</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H64" s="2"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H65" s="2"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H66" s="2"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H67" s="2"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64">
+        <v>5005</v>
+      </c>
+      <c r="D64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="2">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
+        <v>46118.80127314815</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65">
+        <v>4997</v>
+      </c>
+      <c r="D65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="2">
+        <v>0</v>
+      </c>
+      <c r="I65" s="1">
+        <v>46118.80196759259</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66">
+        <v>5069</v>
+      </c>
+      <c r="D66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" t="s">
+        <v>35</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="2">
+        <v>6.2152777777777779E-3</v>
+      </c>
+      <c r="I66" s="1">
+        <v>46118.80196759259</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67">
+        <v>5197</v>
+      </c>
+      <c r="D67" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="I67" s="1">
+        <v>46118.802662037036</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H68" s="2"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H69" s="2"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H70" s="2"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H71" s="2"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H72" s="2"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H73" s="2"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H75" s="2"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H76" s="2"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H77" s="2"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H78" s="2"/>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H79" s="2"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H80" s="2"/>
       <c r="I80" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C21E9EE-15F3-401B-A437-3C797A932D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E140AA-38FA-40D0-850B-0F8182B39AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="36">
   <si>
     <t>Company Name</t>
   </si>
@@ -2124,16 +2124,16 @@
         <v>35</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H59" s="2">
-        <v>0</v>
+        <v>7.3611111111111108E-3</v>
       </c>
       <c r="I59" s="1">
         <v>46118.799189814818</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="s">
         <v>11</v>
@@ -2153,48 +2153,26 @@
         <v>35</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" s="2">
-        <v>0</v>
+        <v>6.828703703703704E-3</v>
       </c>
       <c r="I60" s="1">
         <v>46118.799189814818</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61">
-        <v>5001</v>
-      </c>
-      <c r="D61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="2">
-        <v>3.3912037037037036E-3</v>
-      </c>
-      <c r="I61" s="1">
-        <v>46118.799884259257</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="1"/>
       <c r="K61" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
@@ -2202,10 +2180,10 @@
         <v>34</v>
       </c>
       <c r="C62">
-        <v>4995</v>
+        <v>5001</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
@@ -2214,13 +2192,13 @@
         <v>10</v>
       </c>
       <c r="H62" s="2">
-        <v>8.0902777777777778E-3</v>
+        <v>3.3912037037037036E-3</v>
       </c>
       <c r="I62" s="1">
-        <v>46118.800578703704</v>
+        <v>46118.799884259257</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="s">
         <v>11</v>
@@ -2231,10 +2209,10 @@
         <v>34</v>
       </c>
       <c r="C63">
-        <v>4998</v>
+        <v>4995</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
         <v>35</v>
@@ -2243,7 +2221,7 @@
         <v>10</v>
       </c>
       <c r="H63" s="2">
-        <v>7.3032407407407404E-3</v>
+        <v>8.0902777777777778E-3</v>
       </c>
       <c r="I63" s="1">
         <v>46118.800578703704</v>
@@ -2260,22 +2238,22 @@
         <v>34</v>
       </c>
       <c r="C64">
-        <v>5005</v>
+        <v>4998</v>
       </c>
       <c r="D64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
         <v>35</v>
       </c>
       <c r="G64" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2">
-        <v>0</v>
+        <v>7.3032407407407404E-3</v>
       </c>
       <c r="I64" s="1">
-        <v>46118.80127314815</v>
+        <v>46118.800578703704</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -2289,10 +2267,10 @@
         <v>34</v>
       </c>
       <c r="C65">
-        <v>4997</v>
+        <v>5005</v>
       </c>
       <c r="D65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65" t="s">
         <v>35</v>
@@ -2304,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>46118.80196759259</v>
+        <v>46118.80127314815</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -2318,25 +2296,25 @@
         <v>34</v>
       </c>
       <c r="C66">
-        <v>5069</v>
+        <v>4997</v>
       </c>
       <c r="D66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H66" s="2">
-        <v>6.2152777777777779E-3</v>
+        <v>0</v>
       </c>
       <c r="I66" s="1">
         <v>46118.80196759259</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="s">
         <v>11</v>
@@ -2347,10 +2325,10 @@
         <v>34</v>
       </c>
       <c r="C67">
-        <v>5197</v>
+        <v>5069</v>
       </c>
       <c r="D67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
@@ -2359,10 +2337,10 @@
         <v>10</v>
       </c>
       <c r="H67" s="2">
-        <v>1.6550925925925926E-3</v>
+        <v>6.2152777777777779E-3</v>
       </c>
       <c r="I67" s="1">
-        <v>46118.802662037036</v>
+        <v>46118.80196759259</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -2372,8 +2350,33 @@
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H68" s="2"/>
-      <c r="I68" s="1"/>
+      <c r="B68" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68">
+        <v>5197</v>
+      </c>
+      <c r="D68" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1.6550925925925926E-3</v>
+      </c>
+      <c r="I68" s="1">
+        <v>46118.802662037036</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H69" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E140AA-38FA-40D0-850B-0F8182B39AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4356616E-21E8-40F1-BC8D-998CA141C8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2285,7 +2285,7 @@
         <v>46118.80127314815</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -2305,16 +2305,16 @@
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H66" s="2">
-        <v>0</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I66" s="1">
         <v>46118.80196759259</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4356616E-21E8-40F1-BC8D-998CA141C8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA204D76-2AFA-4510-925C-833F2C8A080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="37">
   <si>
     <t>Company Name</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Rules for Safe Driving</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2288,7 @@
         <v>46118.80127314815</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -2379,48 +2382,323 @@
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H69" s="2"/>
-      <c r="I69" s="1"/>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69">
+        <v>5003</v>
+      </c>
+      <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>46146.714930555558</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H70" s="2"/>
-      <c r="I70" s="1"/>
+      <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70">
+        <v>4996</v>
+      </c>
+      <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="2">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>46146.715624999997</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H71" s="2"/>
-      <c r="I71" s="1"/>
+      <c r="B71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71">
+        <v>5000</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="2">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>46146.716319444444</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H72" s="2"/>
-      <c r="I72" s="1"/>
+      <c r="B72" t="s">
+        <v>34</v>
+      </c>
+      <c r="C72">
+        <v>5004</v>
+      </c>
+      <c r="D72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="2">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>46146.716319444444</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H73" s="2"/>
-      <c r="I73" s="1"/>
+      <c r="B73" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73">
+        <v>5001</v>
+      </c>
+      <c r="D73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="2">
+        <v>6.3310185185185188E-3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>46146.717013888891</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74">
+        <v>4995</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" t="s">
+        <v>36</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
+        <v>46146.717013888891</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H75" s="2"/>
-      <c r="I75" s="1"/>
+      <c r="B75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75">
+        <v>4998</v>
+      </c>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="2">
+        <v>5.3009259259259259E-3</v>
+      </c>
+      <c r="I75" s="1">
+        <v>46146.71770833333</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H76" s="2"/>
-      <c r="I76" s="1"/>
+      <c r="B76" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76">
+        <v>5005</v>
+      </c>
+      <c r="D76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
+        <v>46146.718402777777</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H77" s="2"/>
-      <c r="I77" s="1"/>
+      <c r="B77" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77">
+        <v>4997</v>
+      </c>
+      <c r="D77" t="s">
+        <v>30</v>
+      </c>
+      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="2">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>46146.719097222223</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
+      <c r="B78" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78">
+        <v>5069</v>
+      </c>
+      <c r="D78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78" t="s">
+        <v>10</v>
+      </c>
+      <c r="H78" s="2">
+        <v>5.0810185185185186E-3</v>
+      </c>
+      <c r="I78" s="1">
+        <v>46146.719097222223</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H79" s="2"/>
-      <c r="I79" s="1"/>
+      <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79">
+        <v>5197</v>
+      </c>
+      <c r="D79" t="s">
+        <v>33</v>
+      </c>
+      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="2">
+        <v>4.8263888888888887E-3</v>
+      </c>
+      <c r="I79" s="1">
+        <v>46146.71979166667</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H80" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA204D76-2AFA-4510-925C-833F2C8A080D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC20E0E2-26FB-4B63-82DE-AC7AAFE7B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -2288,7 +2288,7 @@
         <v>46118.80127314815</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -2395,10 +2395,10 @@
         <v>36</v>
       </c>
       <c r="G69" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H69" s="2">
-        <v>0</v>
+        <v>1.4039351851851851E-2</v>
       </c>
       <c r="I69" s="1">
         <v>46146.714930555558</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\T Miller - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4EBD6B-EEB2-4672-B212-2BDAC710B4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD52387-8A56-47E8-9FBB-0DFA8F6901CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -2549,7 +2549,7 @@
         <v>46146.717013888891</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" t="s">
         <v>11</v>
@@ -2607,7 +2607,7 @@
         <v>46146.718402777777</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="s">
         <v>11</v>
@@ -2636,7 +2636,7 @@
         <v>46146.719097222223</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\T Miller - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\t-miller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0237A362-F87E-4D1F-9246-4E2B18C210A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248364EF-7E14-4490-9C37-9AB4D7B38750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2888,7 +2888,7 @@
         <v>12</v>
       </c>
       <c r="H86" s="2">
-        <v>9.432870370370371E-3</v>
+        <v>9.9305555555555553E-3</v>
       </c>
       <c r="I86" s="1">
         <v>46174.649652777778</v>
@@ -2952,16 +2952,16 @@
         <v>21</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>0</v>
+        <v>1.0787037037037038E-2</v>
       </c>
       <c r="I89" s="1">
         <v>46176.430208333331</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" t="s">
         <v>11</v>
@@ -2981,10 +2981,10 @@
         <v>21</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H90" s="2">
-        <v>0</v>
+        <v>6.8391203703703704E-2</v>
       </c>
       <c r="I90" s="1">
         <v>46176.430208333331</v>
@@ -3019,7 +3019,7 @@
         <v>46176.430208333331</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="s">
         <v>11</v>
@@ -3048,7 +3048,7 @@
         <v>46176.430902777778</v>
       </c>
       <c r="J92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\t-miller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{634A7FD0-CA8C-4309-BEBB-85E28993AF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25481BD0-E874-46DB-9FB5-FEA82BEC5C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="40">
   <si>
     <t>Company Name</t>
   </si>
@@ -83,13 +83,13 @@
     <t>PENDING</t>
   </si>
   <si>
-    <t>Speed Management</t>
-  </si>
-  <si>
     <t>Winter Weather</t>
   </si>
   <si>
     <t>Rules for Safe Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Speed Mangement-C</t>
+  </si>
+  <si>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
@@ -529,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -578,16 +581,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>5003</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -607,16 +610,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>4999</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -636,16 +639,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>4996</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>12</v>
@@ -674,16 +677,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>4994</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -703,16 +706,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>5000</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -732,16 +735,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>5004</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -761,16 +764,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>5001</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -790,16 +793,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>5002</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -819,16 +822,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>4995</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
@@ -857,16 +860,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>4998</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -886,16 +889,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>5005</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -915,16 +918,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>4997</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>12</v>
@@ -953,13 +956,13 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17">
         <v>5003</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>19</v>
@@ -982,13 +985,13 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>4999</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>19</v>
@@ -1011,13 +1014,13 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>4996</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>19</v>
@@ -1040,13 +1043,13 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
         <v>5000</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>19</v>
@@ -1069,13 +1072,13 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>5004</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>19</v>
@@ -1107,13 +1110,13 @@
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>5001</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>19</v>
@@ -1145,13 +1148,13 @@
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25">
         <v>5002</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>19</v>
@@ -1174,13 +1177,13 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>4995</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>19</v>
@@ -1203,13 +1206,13 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>4998</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>19</v>
@@ -1232,13 +1235,13 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28">
         <v>5005</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>19</v>
@@ -1261,13 +1264,13 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>4997</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>19</v>
@@ -1290,13 +1293,13 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30">
         <v>5069</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>19</v>
@@ -1319,16 +1322,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E31">
         <v>5003</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1348,16 +1351,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E32">
         <v>4999</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1377,16 +1380,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33">
         <v>4996</v>
       </c>
       <c r="F33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1406,16 +1409,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34">
         <v>5000</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1435,16 +1438,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35">
         <v>5004</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1464,16 +1467,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36">
         <v>5001</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1493,16 +1496,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37">
         <v>5002</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1522,16 +1525,16 @@
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38">
         <v>4995</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1551,16 +1554,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39">
         <v>4998</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1580,16 +1583,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40">
         <v>5005</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1609,16 +1612,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41">
         <v>5193</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1638,16 +1641,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42">
         <v>4997</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1667,16 +1670,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43">
         <v>5069</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1696,16 +1699,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44">
         <v>5197</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1725,13 +1728,13 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45">
         <v>5003</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>17</v>
@@ -1754,13 +1757,13 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E46">
         <v>4996</v>
       </c>
       <c r="F46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>17</v>
@@ -1783,13 +1786,13 @@
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47">
         <v>5000</v>
       </c>
       <c r="F47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>17</v>
@@ -1812,13 +1815,13 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48">
         <v>5004</v>
       </c>
       <c r="F48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>17</v>
@@ -1841,13 +1844,13 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49">
         <v>5001</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>17</v>
@@ -1870,13 +1873,13 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50">
         <v>4995</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>17</v>
@@ -1899,13 +1902,13 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51">
         <v>4998</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>17</v>
@@ -1928,13 +1931,13 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52">
         <v>5005</v>
       </c>
       <c r="F52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>17</v>
@@ -1957,13 +1960,13 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53">
         <v>5193</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>17</v>
@@ -1986,13 +1989,13 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54">
         <v>4997</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>17</v>
@@ -2015,13 +2018,13 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55">
         <v>5069</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>17</v>
@@ -2044,13 +2047,13 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56">
         <v>5197</v>
       </c>
       <c r="F56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>17</v>
@@ -2073,13 +2076,13 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57">
         <v>5003</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>20</v>
@@ -2102,13 +2105,13 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58">
         <v>4996</v>
       </c>
       <c r="F58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>20</v>
@@ -2131,13 +2134,13 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59">
         <v>5000</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>20</v>
@@ -2160,13 +2163,13 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60">
         <v>5004</v>
       </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>20</v>
@@ -2198,13 +2201,13 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E62">
         <v>5001</v>
       </c>
       <c r="F62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>20</v>
@@ -2227,13 +2230,13 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E63">
         <v>4995</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>20</v>
@@ -2256,13 +2259,13 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64">
         <v>4998</v>
       </c>
       <c r="F64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>20</v>
@@ -2285,13 +2288,13 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65">
         <v>5005</v>
       </c>
       <c r="F65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>20</v>
@@ -2314,13 +2317,13 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66">
         <v>4997</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>20</v>
@@ -2343,13 +2346,13 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67">
         <v>5069</v>
       </c>
       <c r="F67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>20</v>
@@ -2372,13 +2375,13 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68">
         <v>5197</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>20</v>
@@ -2401,16 +2404,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69">
         <v>5003</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2430,16 +2433,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E70">
         <v>4996</v>
       </c>
       <c r="F70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2459,16 +2462,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71">
         <v>5000</v>
       </c>
       <c r="F71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2488,16 +2491,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E72">
         <v>5004</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2517,16 +2520,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73">
         <v>5001</v>
       </c>
       <c r="F73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2546,16 +2549,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E74">
         <v>4995</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2575,16 +2578,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E75">
         <v>4998</v>
       </c>
       <c r="F75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2604,16 +2607,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E76">
         <v>5005</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2633,16 +2636,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E77">
         <v>4997</v>
       </c>
       <c r="F77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>12</v>
@@ -2671,16 +2674,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E79">
         <v>5069</v>
       </c>
       <c r="F79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2700,16 +2703,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E80">
         <v>5197</v>
       </c>
       <c r="F80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2729,16 +2732,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E81">
         <v>5003</v>
       </c>
       <c r="F81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2758,16 +2761,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E82">
         <v>4996</v>
       </c>
       <c r="F82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2787,16 +2790,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E83">
         <v>5001</v>
       </c>
       <c r="F83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2816,16 +2819,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E84">
         <v>4998</v>
       </c>
       <c r="F84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2845,16 +2848,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E85">
         <v>5005</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2874,16 +2877,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E86">
         <v>5069</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>12</v>
@@ -2912,16 +2915,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E88">
         <v>5197</v>
       </c>
       <c r="F88" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -2941,13 +2944,13 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E89">
         <v>5000</v>
       </c>
       <c r="F89" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>21</v>
@@ -2970,13 +2973,13 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E90">
         <v>5004</v>
       </c>
       <c r="F90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>21</v>
@@ -2999,13 +3002,13 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E91">
         <v>4995</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>21</v>
@@ -3028,13 +3031,13 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E92">
         <v>4997</v>
       </c>
       <c r="F92" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>21</v>
@@ -3056,120 +3059,327 @@
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="1"/>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93">
+        <v>5003</v>
+      </c>
+      <c r="F93" t="s">
+        <v>25</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J93" s="2">
+        <v>9.6759259259259264E-3</v>
+      </c>
+      <c r="K93" s="1">
+        <v>46212.754629629628</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="1"/>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94">
+        <v>4996</v>
+      </c>
+      <c r="F94" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1">
+        <v>46212.755324074074</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H95" s="2"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="1"/>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95">
+        <v>5000</v>
+      </c>
+      <c r="F95" t="s">
+        <v>29</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0</v>
+      </c>
+      <c r="K95" s="1">
+        <v>46212.755324074074</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H96" s="2"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H97" s="2"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H98" s="2"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H101" s="2"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="1"/>
-    </row>
-    <row r="102" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96">
+        <v>5004</v>
+      </c>
+      <c r="F96" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1">
+        <v>46212.756018518521</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97">
+        <v>5001</v>
+      </c>
+      <c r="F97" t="s">
+        <v>31</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1">
+        <v>46212.756712962961</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98">
+        <v>4995</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1">
+        <v>46212.757407407407</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99">
+        <v>4998</v>
+      </c>
+      <c r="F99" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J99" s="2">
+        <v>6.7245370370370367E-3</v>
+      </c>
+      <c r="K99" s="1">
+        <v>46212.757407407407</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100">
+        <v>5069</v>
+      </c>
+      <c r="F100" t="s">
+        <v>37</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J100" s="2">
+        <v>6.3541666666666668E-3</v>
+      </c>
+      <c r="K100" s="1">
+        <v>46212.758101851854</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101">
+        <v>5197</v>
+      </c>
+      <c r="F101" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="2">
+        <v>5.8796296296296296E-3</v>
+      </c>
+      <c r="K101" s="1">
+        <v>46212.758796296293</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H102" s="2"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H103" s="2"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
       <c r="K103" s="1"/>
     </row>
-    <row r="104" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H104" s="2"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H105" s="2"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H106" s="2"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
       <c r="K106" s="1"/>
     </row>
-    <row r="107" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H107" s="2"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
       <c r="K107" s="1"/>
     </row>
-    <row r="108" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H108" s="2"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
     </row>
-    <row r="109" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H109" s="2"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
       <c r="K109" s="1"/>
     </row>
-    <row r="110" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H110" s="2"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
       <c r="K110" s="1"/>
     </row>
-    <row r="111" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H111" s="2"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -40980,7 +41190,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\t-miller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25481BD0-E874-46DB-9FB5-FEA82BEC5C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F694945-2011-40BB-BB6E-8CB56E2AF6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -83,6 +83,12 @@
     <t>PENDING</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -92,25 +98,19 @@
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>Speed Management</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>T Miller</t>
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -619,7 +619,7 @@
         <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -648,7 +648,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>12</v>
@@ -672,7 +672,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="M5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
@@ -686,7 +686,7 @@
         <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>13</v>
@@ -715,7 +715,7 @@
         <v>29</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -744,7 +744,7 @@
         <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>13</v>
@@ -773,7 +773,7 @@
         <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>13</v>
@@ -802,7 +802,7 @@
         <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -831,7 +831,7 @@
         <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
@@ -855,7 +855,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="1"/>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
@@ -869,7 +869,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>35</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>13</v>
@@ -927,7 +927,7 @@
         <v>36</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>12</v>
@@ -951,7 +951,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="M16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>13</v>
@@ -994,7 +994,7 @@
         <v>26</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>27</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1052,7 +1052,7 @@
         <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1105,7 +1105,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
@@ -1119,7 +1119,7 @@
         <v>31</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>12</v>
@@ -1143,7 +1143,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="1"/>
       <c r="M24" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
@@ -1157,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>13</v>
@@ -1186,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1215,7 +1215,7 @@
         <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1244,7 +1244,7 @@
         <v>35</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1273,7 +1273,7 @@
         <v>36</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1302,7 +1302,7 @@
         <v>37</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1331,7 +1331,7 @@
         <v>25</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1360,7 +1360,7 @@
         <v>26</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1389,7 +1389,7 @@
         <v>27</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1418,7 +1418,7 @@
         <v>29</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1447,7 +1447,7 @@
         <v>30</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1476,7 +1476,7 @@
         <v>31</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>13</v>
@@ -1534,7 +1534,7 @@
         <v>33</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
@@ -1563,7 +1563,7 @@
         <v>34</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1592,7 +1592,7 @@
         <v>35</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1621,7 +1621,7 @@
         <v>38</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1650,7 +1650,7 @@
         <v>36</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1679,7 +1679,7 @@
         <v>37</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>39</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1737,7 +1737,7 @@
         <v>25</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1766,7 +1766,7 @@
         <v>27</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
@@ -1795,7 +1795,7 @@
         <v>29</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1824,7 +1824,7 @@
         <v>30</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1853,7 +1853,7 @@
         <v>31</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1882,7 +1882,7 @@
         <v>33</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>34</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1940,7 +1940,7 @@
         <v>35</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>36</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>37</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2056,7 +2056,7 @@
         <v>39</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>25</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2114,7 +2114,7 @@
         <v>27</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>29</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2172,7 +2172,7 @@
         <v>30</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>12</v>
@@ -2196,7 +2196,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
@@ -2210,7 +2210,7 @@
         <v>31</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2239,7 +2239,7 @@
         <v>33</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2268,7 +2268,7 @@
         <v>34</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>35</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>13</v>
@@ -2326,7 +2326,7 @@
         <v>36</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2355,7 +2355,7 @@
         <v>37</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2384,7 +2384,7 @@
         <v>39</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2413,7 +2413,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>27</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2471,7 +2471,7 @@
         <v>29</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>30</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2529,7 +2529,7 @@
         <v>31</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2558,7 +2558,7 @@
         <v>33</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2587,7 +2587,7 @@
         <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2616,7 +2616,7 @@
         <v>35</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2645,7 +2645,7 @@
         <v>36</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>12</v>
@@ -2669,7 +2669,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2683,7 +2683,7 @@
         <v>37</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2712,7 +2712,7 @@
         <v>39</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2741,7 +2741,7 @@
         <v>25</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>27</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2799,7 +2799,7 @@
         <v>31</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2828,7 +2828,7 @@
         <v>34</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2857,7 +2857,7 @@
         <v>35</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2886,7 +2886,7 @@
         <v>37</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>12</v>
@@ -2910,7 +2910,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="1"/>
       <c r="M87" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
@@ -2924,7 +2924,7 @@
         <v>39</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -2953,7 +2953,7 @@
         <v>29</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -2982,7 +2982,7 @@
         <v>30</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3011,7 +3011,7 @@
         <v>33</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3040,7 +3040,7 @@
         <v>36</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3069,7 +3069,7 @@
         <v>25</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3098,7 +3098,7 @@
         <v>27</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3127,7 +3127,7 @@
         <v>29</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>13</v>
@@ -3156,13 +3156,13 @@
         <v>30</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J96" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="K96" s="1">
         <v>46212.756018518521</v>
@@ -3185,7 +3185,7 @@
         <v>31</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3214,7 +3214,7 @@
         <v>33</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>13</v>
@@ -3243,7 +3243,7 @@
         <v>34</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3272,7 +3272,7 @@
         <v>37</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3301,7 +3301,7 @@
         <v>39</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -10880,6 +10880,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -14203,6 +14204,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -14213,14 +14215,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -14246,6 +14251,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -14255,9 +14261,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -41195,6 +41203,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -41202,6 +41211,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -41209,6 +41219,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -41224,6 +41235,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -41233,6 +41245,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -41240,9 +41253,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -41250,12 +41269,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -41263,12 +41285,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -41280,9 +41305,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -41297,6 +41324,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -41323,6 +41351,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -41333,7 +41362,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -41341,6 +41375,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -41352,6 +41387,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -41359,6 +41395,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -41373,13 +41410,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -41390,15 +41433,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -41414,6 +41460,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -41432,6 +41479,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -41443,6 +41491,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -41460,18 +41509,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -41500,6 +41554,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -41507,9 +41562,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -41532,12 +41589,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -41552,9 +41612,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -41570,12 +41632,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -41596,6 +41660,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -41607,9 +41672,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -41621,6 +41688,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -41660,9 +41728,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -41670,9 +41740,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -41683,6 +41755,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -41690,18 +41763,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -41709,6 +41790,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -41719,6 +41801,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -41745,15 +41828,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -41775,6 +41862,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -41782,9 +41870,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -41792,6 +41882,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -41803,6 +41894,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -41817,6 +41909,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -41826,6 +41922,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -41837,6 +41934,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -41847,10 +41945,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -41858,6 +41961,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -41872,6 +41976,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -41894,6 +41999,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -41913,25 +42019,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -41939,6 +42057,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -41946,15 +42065,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -41968,6 +42094,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -41986,9 +42113,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -41996,9 +42125,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -42006,6 +42137,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -42022,10 +42154,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
